--- a/translations/welsh-translations/xlsx/07-producer-certificate-submit.xlsx
+++ b/translations/welsh-translations/xlsx/07-producer-certificate-submit.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="110">
   <si>
     <t>Translator notes</t>
   </si>
@@ -103,27 +103,12 @@
     <t>If any information on this page is incorrect, contact the {{regulatorName}}:</t>
   </si>
   <si>
-    <t>compliance.components.overallStatus.recyclingObligationsHeading</t>
+    <t>compliance.components.obligationsTable.recyclingObligationsHeading</t>
   </si>
   <si>
     <t>Recycling obligations</t>
   </si>
   <si>
-    <t>compliance.components.overallStatus.overallMet</t>
-  </si>
-  <si>
-    <t>Recycling obligations have been met</t>
-  </si>
-  <si>
-    <t>compliance.components.overallStatus.overallNotMet</t>
-  </si>
-  <si>
-    <t>Recycling obligations have not been met</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.recyclingObligationsHeading</t>
-  </si>
-  <si>
     <t>compliance.components.obligationsTable.tonnesNote</t>
   </si>
   <si>
@@ -172,6 +157,12 @@
     <t>Status</t>
   </si>
   <si>
+    <t>compliance.components.obligationsTable.notAvailableYet</t>
+  </si>
+  <si>
+    <t>Not available yet</t>
+  </si>
+  <si>
     <t>compliance.components.obligationsTable.material.paperComposite</t>
   </si>
   <si>
@@ -241,19 +232,19 @@
     <t>compliance.components.obligationsTable.obligationStatus.met</t>
   </si>
   <si>
-    <t>MET</t>
+    <t>Met</t>
   </si>
   <si>
     <t>compliance.components.obligationsTable.obligationStatus.notMet</t>
   </si>
   <si>
-    <t>NOT MET</t>
+    <t>Not met</t>
   </si>
   <si>
     <t>compliance.components.obligationsTable.obligationStatus.noDataYet</t>
   </si>
   <si>
-    <t>NO DATA YET</t>
+    <t>No data yet</t>
   </si>
   <si>
     <t>compliance.components.declaration.heading</t>
@@ -748,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -1050,7 +1041,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>13</v>
@@ -1061,7 +1052,7 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>10</v>
@@ -1070,7 +1061,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>13</v>
@@ -1081,7 +1072,7 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>10</v>
@@ -1090,7 +1081,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>13</v>
@@ -1101,7 +1092,7 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>10</v>
@@ -1110,7 +1101,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>13</v>
@@ -1121,7 +1112,7 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>10</v>
@@ -1130,7 +1121,7 @@
         <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>13</v>
@@ -1141,7 +1132,7 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>10</v>
@@ -1150,7 +1141,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>13</v>
@@ -1161,7 +1152,7 @@
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>10</v>
@@ -1170,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>13</v>
@@ -1181,7 +1172,7 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>10</v>
@@ -1190,7 +1181,7 @@
         <v>11</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>13</v>
@@ -1201,7 +1192,7 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>10</v>
@@ -1210,7 +1201,7 @@
         <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>13</v>
@@ -1221,7 +1212,7 @@
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>10</v>
@@ -1230,7 +1221,7 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>13</v>
@@ -1241,7 +1232,7 @@
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>10</v>
@@ -1250,7 +1241,7 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>13</v>
@@ -1261,7 +1252,7 @@
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>10</v>
@@ -1270,7 +1261,7 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>13</v>
@@ -1281,7 +1272,7 @@
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>10</v>
@@ -1290,7 +1281,7 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>13</v>
@@ -1301,7 +1292,7 @@
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>10</v>
@@ -1310,7 +1301,7 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>13</v>
@@ -1321,7 +1312,7 @@
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>10</v>
@@ -1330,7 +1321,7 @@
         <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>13</v>
@@ -1341,7 +1332,7 @@
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
@@ -1350,7 +1341,7 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>13</v>
@@ -1361,7 +1352,7 @@
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>10</v>
@@ -1370,7 +1361,7 @@
         <v>11</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>13</v>
@@ -1381,7 +1372,7 @@
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>10</v>
@@ -1390,7 +1381,7 @@
         <v>11</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>13</v>
@@ -1401,7 +1392,7 @@
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>10</v>
@@ -1410,7 +1401,7 @@
         <v>11</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>13</v>
@@ -1421,7 +1412,7 @@
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>10</v>
@@ -1430,7 +1421,7 @@
         <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>13</v>
@@ -1441,7 +1432,7 @@
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>10</v>
@@ -1450,7 +1441,7 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>13</v>
@@ -1461,7 +1452,7 @@
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>10</v>
@@ -1470,7 +1461,7 @@
         <v>11</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>13</v>
@@ -1481,7 +1472,7 @@
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>10</v>
@@ -1490,7 +1481,7 @@
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>13</v>
@@ -1499,9 +1490,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>10</v>
@@ -1510,7 +1501,7 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>13</v>
@@ -1521,7 +1512,7 @@
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>10</v>
@@ -1530,7 +1521,7 @@
         <v>11</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>13</v>
@@ -1539,9 +1530,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>10</v>
@@ -1550,7 +1541,7 @@
         <v>11</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>13</v>
@@ -1561,7 +1552,7 @@
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>10</v>
@@ -1570,7 +1561,7 @@
         <v>11</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>13</v>
@@ -1581,7 +1572,7 @@
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>10</v>
@@ -1590,7 +1581,7 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>13</v>
@@ -1601,7 +1592,7 @@
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>10</v>
@@ -1610,7 +1601,7 @@
         <v>11</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>13</v>
@@ -1621,7 +1612,7 @@
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>10</v>
@@ -1630,7 +1621,7 @@
         <v>11</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>13</v>
@@ -1641,7 +1632,7 @@
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>10</v>
@@ -1650,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>13</v>
@@ -1661,7 +1652,7 @@
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>10</v>
@@ -1670,7 +1661,7 @@
         <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>13</v>
@@ -1681,7 +1672,7 @@
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>10</v>
@@ -1690,7 +1681,7 @@
         <v>11</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>13</v>
@@ -1701,7 +1692,7 @@
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>10</v>
@@ -1710,7 +1701,7 @@
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>13</v>
@@ -1721,7 +1712,7 @@
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>10</v>
@@ -1730,7 +1721,7 @@
         <v>11</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>13</v>
@@ -1741,7 +1732,7 @@
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>10</v>
@@ -1750,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>13</v>
@@ -1761,7 +1752,7 @@
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>10</v>
@@ -1770,7 +1761,7 @@
         <v>11</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>13</v>
@@ -1779,48 +1770,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:F56"/>
+  <autoFilter ref="A5:F54"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>

--- a/translations/welsh-translations/xlsx/07-producer-certificate-submit.xlsx
+++ b/translations/welsh-translations/xlsx/07-producer-certificate-submit.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="113">
   <si>
     <t>Translator notes</t>
   </si>
@@ -55,12 +55,27 @@
     <t/>
   </si>
   <si>
+    <t>https://www.figma.com/design/eG3Z7k6gmh9ZCtooRy0iBz/Certificate-Statement-of-Certification?node-id=4297-32941&amp;t=i61f1BsSBR1bSqaq-4</t>
+  </si>
+  <si>
     <t>compliance.certificateSubmit.heading</t>
   </si>
   <si>
     <t>Check and submit your {{year}} certificate of compliance</t>
   </si>
   <si>
+    <t>common.errorSummary.title</t>
+  </si>
+  <si>
+    <t>There is a problem</t>
+  </si>
+  <si>
+    <t>compliance.components.regulatorInset.insetLead</t>
+  </si>
+  <si>
+    <t>If any information on this page is incorrect, contact {{regulatorName}}:</t>
+  </si>
+  <si>
     <t>compliance.components.summaryList.heading</t>
   </si>
   <si>
@@ -97,12 +112,6 @@
     <t>Regulator</t>
   </si>
   <si>
-    <t>compliance.components.regulatorInset.insetLead</t>
-  </si>
-  <si>
-    <t>If any information on this page is incorrect, contact the {{regulatorName}}:</t>
-  </si>
-  <si>
     <t>compliance.components.obligationsTable.recyclingObligationsHeading</t>
   </si>
   <si>
@@ -115,46 +124,154 @@
     <t>All values are shown in whole tonnes.</t>
   </si>
   <si>
+    <t>compliance.components.obligationsTable.tableMaterial</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableObligationToMeet</t>
+  </si>
+  <si>
+    <t>Recycling obligations to meet</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableAwaiting</t>
+  </si>
+  <si>
+    <t>Tonnage awaiting acceptance</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableAccepted</t>
+  </si>
+  <si>
+    <t>Tonnage accepted</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableOutstanding</t>
+  </si>
+  <si>
+    <t>Tonnage outstanding</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.tableStatus</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>compliance.components.obligationsTable.glassHeading</t>
   </si>
   <si>
     <t>Glass recycling obligation breakdown</t>
   </si>
   <si>
-    <t>compliance.components.obligationsTable.tableMaterial</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.tableObligationToMeet</t>
-  </si>
-  <si>
-    <t>Recycling obligations to meet</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.tableAwaiting</t>
-  </si>
-  <si>
-    <t>Tonnage awaiting acceptance</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.tableAccepted</t>
-  </si>
-  <si>
-    <t>Tonnage accepted</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.tableOutstanding</t>
-  </si>
-  <si>
-    <t>Tonnage outstanding</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.tableStatus</t>
-  </si>
-  <si>
-    <t>Status</t>
+    <t>compliance.components.declaration.heading</t>
+  </si>
+  <si>
+    <t>Declaration</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.intro</t>
+  </si>
+  <si>
+    <t>By entering your name and submitting this certificate of compliance, you are verifying:</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.bullet1</t>
+  </si>
+  <si>
+    <t>you are an approved or delegated person who is eligible to submit this certificate of compliance on behalf of {{organisationName}}</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.bullet2</t>
+  </si>
+  <si>
+    <t>the information you are submitting is accurate</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.bullet3</t>
+  </si>
+  <si>
+    <t>you understand that you may face enforcement action if you submit false or misleading information</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.fullNameLabel</t>
+  </si>
+  <si>
+    <t>Your full name</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.submitButton</t>
+  </si>
+  <si>
+    <t>Confirm and submit</t>
+  </si>
+  <si>
+    <t>compliance.components.declaration.cancelLink</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.paperComposite</t>
+  </si>
+  <si>
+    <t>Paper, board or fibre-based composite material</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.plastic</t>
+  </si>
+  <si>
+    <t>Plastic</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.wood</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.steel</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.aluminium</t>
+  </si>
+  <si>
+    <t>Aluminium</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.glass</t>
+  </si>
+  <si>
+    <t>Glass</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.glassRemelt</t>
+  </si>
+  <si>
+    <t>Glass remelt</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.glassRemaining</t>
+  </si>
+  <si>
+    <t>Remaining glass</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.material.default</t>
+  </si>
+  <si>
+    <t>{{name}}</t>
   </si>
   <si>
     <t>compliance.components.obligationsTable.notAvailableYet</t>
@@ -163,136 +280,28 @@
     <t>Not available yet</t>
   </si>
   <si>
-    <t>compliance.components.obligationsTable.material.paperComposite</t>
-  </si>
-  <si>
-    <t>Paper, board or fibre-based composite material</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.plastic</t>
-  </si>
-  <si>
-    <t>Plastic</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.wood</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.steel</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.aluminium</t>
-  </si>
-  <si>
-    <t>Aluminium</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.glass</t>
-  </si>
-  <si>
-    <t>Glass</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.glassRemelt</t>
-  </si>
-  <si>
-    <t>Glass remelt</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.glassRemaining</t>
-  </si>
-  <si>
-    <t>Remaining glass</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.other</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.material.default</t>
-  </si>
-  <si>
-    <t>{{name}}</t>
+    <t>compliance.components.obligationsTable.obligationStatus.met</t>
+  </si>
+  <si>
+    <t>Met</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.obligationStatus.notMet</t>
+  </si>
+  <si>
+    <t>Not met</t>
+  </si>
+  <si>
+    <t>compliance.components.obligationsTable.obligationStatus.noDataYet</t>
+  </si>
+  <si>
+    <t>No data yet</t>
   </si>
   <si>
     <t>compliance.components.obligationsTable.table.totalsRow</t>
   </si>
   <si>
     <t>Totals</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.obligationStatus.met</t>
-  </si>
-  <si>
-    <t>Met</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.obligationStatus.notMet</t>
-  </si>
-  <si>
-    <t>Not met</t>
-  </si>
-  <si>
-    <t>compliance.components.obligationsTable.obligationStatus.noDataYet</t>
-  </si>
-  <si>
-    <t>No data yet</t>
-  </si>
-  <si>
-    <t>compliance.components.declaration.heading</t>
-  </si>
-  <si>
-    <t>Declaration</t>
-  </si>
-  <si>
-    <t>compliance.components.declaration.intro</t>
-  </si>
-  <si>
-    <t>By entering your name and submitting this certificate of compliance, you are verifying:</t>
-  </si>
-  <si>
-    <t>compliance.components.declaration.bullet1</t>
-  </si>
-  <si>
-    <t>you are an approved or delegated person who is eligible to submit this certificate of compliance on behalf of {{organisationName}}</t>
-  </si>
-  <si>
-    <t>compliance.components.declaration.bullet2</t>
-  </si>
-  <si>
-    <t>the information you are submitting is accurate</t>
-  </si>
-  <si>
-    <t>compliance.components.declaration.bullet3</t>
-  </si>
-  <si>
-    <t>you understand that you may face enforcement action if you submit false or misleading information</t>
-  </si>
-  <si>
-    <t>compliance.components.declaration.fullNameLabel</t>
-  </si>
-  <si>
-    <t>Your full name</t>
-  </si>
-  <si>
-    <t>compliance.components.declaration.submitButton</t>
-  </si>
-  <si>
-    <t>Confirm and submit</t>
-  </si>
-  <si>
-    <t>compliance.components.declaration.cancelLink</t>
-  </si>
-  <si>
-    <t>Cancel</t>
   </si>
   <si>
     <t>compliance.errors.submitDeclaration</t>
@@ -739,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -790,7 +799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -807,12 +816,12 @@
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -821,7 +830,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>13</v>
@@ -832,7 +841,7 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -841,7 +850,7 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>13</v>
@@ -852,7 +861,7 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -861,7 +870,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>13</v>
@@ -872,7 +881,7 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -881,7 +890,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>13</v>
@@ -892,7 +901,7 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -901,7 +910,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>13</v>
@@ -912,7 +921,7 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -921,7 +930,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
@@ -932,7 +941,7 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -941,7 +950,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>13</v>
@@ -952,7 +961,7 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
@@ -961,7 +970,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>13</v>
@@ -972,7 +981,7 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>10</v>
@@ -981,7 +990,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>13</v>
@@ -992,7 +1001,7 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
@@ -1001,7 +1010,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>13</v>
@@ -1012,7 +1021,7 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>10</v>
@@ -1021,7 +1030,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>13</v>
@@ -1032,7 +1041,7 @@
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>10</v>
@@ -1041,7 +1050,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>13</v>
@@ -1052,7 +1061,7 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>10</v>
@@ -1061,7 +1070,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>13</v>
@@ -1072,7 +1081,7 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>10</v>
@@ -1081,7 +1090,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>13</v>
@@ -1092,7 +1101,7 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>10</v>
@@ -1101,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>13</v>
@@ -1112,7 +1121,7 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>10</v>
@@ -1121,7 +1130,7 @@
         <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>13</v>
@@ -1132,7 +1141,7 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>10</v>
@@ -1141,7 +1150,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>13</v>
@@ -1152,7 +1161,7 @@
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>10</v>
@@ -1161,7 +1170,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>13</v>
@@ -1172,7 +1181,7 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>10</v>
@@ -1181,7 +1190,7 @@
         <v>11</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>13</v>
@@ -1192,7 +1201,7 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>10</v>
@@ -1201,7 +1210,7 @@
         <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>13</v>
@@ -1210,9 +1219,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>10</v>
@@ -1221,7 +1230,7 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>13</v>
@@ -1232,7 +1241,7 @@
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>10</v>
@@ -1241,7 +1250,7 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>13</v>
@@ -1252,7 +1261,7 @@
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>10</v>
@@ -1261,7 +1270,7 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>13</v>
@@ -1272,7 +1281,7 @@
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>10</v>
@@ -1281,7 +1290,7 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>13</v>
@@ -1292,7 +1301,7 @@
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>10</v>
@@ -1301,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>13</v>
@@ -1312,7 +1321,7 @@
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>10</v>
@@ -1321,7 +1330,7 @@
         <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>13</v>
@@ -1332,7 +1341,7 @@
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
@@ -1341,7 +1350,7 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>13</v>
@@ -1352,7 +1361,7 @@
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>10</v>
@@ -1361,7 +1370,7 @@
         <v>11</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>13</v>
@@ -1372,7 +1381,7 @@
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>10</v>
@@ -1381,7 +1390,7 @@
         <v>11</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>13</v>
@@ -1392,7 +1401,7 @@
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>10</v>
@@ -1401,7 +1410,7 @@
         <v>11</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>13</v>
@@ -1412,7 +1421,7 @@
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>10</v>
@@ -1421,7 +1430,7 @@
         <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>13</v>
@@ -1432,7 +1441,7 @@
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>10</v>
@@ -1441,7 +1450,7 @@
         <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>13</v>
@@ -1452,7 +1461,7 @@
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>10</v>
@@ -1461,7 +1470,7 @@
         <v>11</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>13</v>
@@ -1472,7 +1481,7 @@
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>10</v>
@@ -1481,7 +1490,7 @@
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>13</v>
@@ -1490,9 +1499,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>10</v>
@@ -1501,7 +1510,7 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>13</v>
@@ -1512,7 +1521,7 @@
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>10</v>
@@ -1521,7 +1530,7 @@
         <v>11</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>13</v>
@@ -1532,7 +1541,7 @@
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>10</v>
@@ -1541,7 +1550,7 @@
         <v>11</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>13</v>
@@ -1552,7 +1561,7 @@
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>10</v>
@@ -1561,7 +1570,7 @@
         <v>11</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>13</v>
@@ -1572,7 +1581,7 @@
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>10</v>
@@ -1581,7 +1590,7 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>13</v>
@@ -1592,7 +1601,7 @@
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>10</v>
@@ -1601,7 +1610,7 @@
         <v>11</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>13</v>
@@ -1612,7 +1621,7 @@
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>10</v>
@@ -1621,7 +1630,7 @@
         <v>11</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>13</v>
@@ -1632,7 +1641,7 @@
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>10</v>
@@ -1641,7 +1650,7 @@
         <v>11</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>13</v>
@@ -1652,7 +1661,7 @@
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>10</v>
@@ -1661,7 +1670,7 @@
         <v>11</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>13</v>
@@ -1672,7 +1681,7 @@
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>10</v>
@@ -1681,7 +1690,7 @@
         <v>11</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>13</v>
@@ -1692,7 +1701,7 @@
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>10</v>
@@ -1701,7 +1710,7 @@
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>13</v>
@@ -1712,7 +1721,7 @@
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>10</v>
@@ -1721,7 +1730,7 @@
         <v>11</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>13</v>
@@ -1732,7 +1741,7 @@
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>10</v>
@@ -1741,7 +1750,7 @@
         <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>13</v>
@@ -1752,7 +1761,7 @@
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>10</v>
@@ -1761,7 +1770,7 @@
         <v>11</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>13</v>
@@ -1770,13 +1779,36 @@
         <v>13</v>
       </c>
     </row>
+    <row r="55" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:F54"/>
+  <autoFilter ref="A5:F55"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F6" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/translations/welsh-translations/xlsx/07-producer-certificate-submit.xlsx
+++ b/translations/welsh-translations/xlsx/07-producer-certificate-submit.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A315A4AD-2955-484A-9A5B-180BC7727330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
+    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="163">
   <si>
     <t>Translator notes</t>
   </si>
@@ -350,27 +354,182 @@
   </si>
   <si>
     <t>Your name cannot contain these characters: @, #, $, %, &amp;, &lt;, &gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the Figma file for the full page content. Text that is repeated within the service may be translated in another file and omitted here. </t>
+  </si>
+  <si>
+    <t>Gwirio a chyflwyno eich tystysgrif cydymffurfio</t>
+  </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>Os oes unrhyw wybodaeth anghywir ar y dudalen hon, cysylltwch â {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>Manylion y sefydliad</t>
+  </si>
+  <si>
+    <t>Enw’r sefydliad</t>
+  </si>
+  <si>
+    <t>ID y Sefydliad</t>
+  </si>
+  <si>
+    <t>Cyfeiriad</t>
+  </si>
+  <si>
+    <t>Enw ar y cyfrif</t>
+  </si>
+  <si>
+    <t>Rheoleiddiwr</t>
+  </si>
+  <si>
+    <t>Rhwymedigaethau ailgylchu</t>
+  </si>
+  <si>
+    <t>Mae’r holl werthoedd yn cael eu dangos fel tunelli cyfan.</t>
+  </si>
+  <si>
+    <t>Deunydd</t>
+  </si>
+  <si>
+    <t>Rhwymedigaethau ailgylchu i’w cyflawni</t>
+  </si>
+  <si>
+    <t>Tunelli sy’n aros i gael eu derbyn</t>
+  </si>
+  <si>
+    <t>Tunelli sy’n aros</t>
+  </si>
+  <si>
+    <t>Statws</t>
+  </si>
+  <si>
+    <t>Dadansoddiad o’r rhwymedigaeth ailgylchu gwydr</t>
+  </si>
+  <si>
+    <t>Datganiad</t>
+  </si>
+  <si>
+    <t>Drwy roi eich enw a chyflwyno’r dystysgrif cydymffurfio hon, rydych chi’n cadarnhau:</t>
+  </si>
+  <si>
+    <t>eich bod chi’n berson cymeradwy neu ddirprwyedig sy’n gymwys i gyflwyno’r dystysgrif cydymffurfio hon ar ran {{organisationName}}</t>
+  </si>
+  <si>
+    <t>bod yr wybodaeth rydych chi’n ei chyflwyno yn gywir</t>
+  </si>
+  <si>
+    <t>eich bod yn deall y gallech wynebu camau gorfodi os byddwch yn cyflwyno gwybodaeth anwir neu gamarweiniol</t>
+  </si>
+  <si>
+    <t>Eich enw llawn</t>
+  </si>
+  <si>
+    <t>Cadarnhau a chyflwyno</t>
+  </si>
+  <si>
+    <t>Canslo</t>
+  </si>
+  <si>
+    <t>Papur, cardfwrdd neu ddeunydd cyfansawdd ffeibr</t>
+  </si>
+  <si>
+    <t>Plastig</t>
+  </si>
+  <si>
+    <t>Pren</t>
+  </si>
+  <si>
+    <t>Dur</t>
+  </si>
+  <si>
+    <t>Alwminiwm</t>
+  </si>
+  <si>
+    <t>Gwydr</t>
+  </si>
+  <si>
+    <t>Gwydr aildoddi</t>
+  </si>
+  <si>
+    <t>Gwydr sy’n weddill</t>
+  </si>
+  <si>
+    <t>Arall</t>
+  </si>
+  <si>
+    <t>Ddim ar gael eto</t>
+  </si>
+  <si>
+    <t>Cyflawnwyd</t>
+  </si>
+  <si>
+    <t>Dim data eto</t>
+  </si>
+  <si>
+    <t>Cyfansymiau</t>
+  </si>
+  <si>
+    <t>Does dim modd cyflwyno datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>Does dim modd paratoi tystysgrif cydymffurfio</t>
+  </si>
+  <si>
+    <t>Does dim modd paratoi datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>Does dim modd canfod cyflwyno prif lwyth storfa ar gyfer y flwyddyn {{year}}</t>
+  </si>
+  <si>
+    <t>Rhaid i chi roi eich enw llawn</t>
+  </si>
+  <si>
+    <t>Rhaid i’ch enw fod yn fwy nag un nod</t>
+  </si>
+  <si>
+    <t>Rhaid i’ch enw fod yn llai na 255 nod</t>
+  </si>
+  <si>
+    <t>Does dim modd i’ch enw gynnwys y nodau hyn: @, #, $, %, &amp;, &lt;, &gt;</t>
+  </si>
+  <si>
+    <t>Gwirio a chyflwyno eich tystysgrif cydymffurfio ar gyfer {{year}}</t>
+  </si>
+  <si>
+    <t>Tunelli sydd wedi’u derbyn</t>
+  </si>
+  <si>
+    <t>Heb gyflawni</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -398,15 +557,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -747,9 +912,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -757,1059 +922,1064 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E7" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="E8" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="E9" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="E10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="E11" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="E12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="E13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="E14" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="E15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="E16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="E17" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="E18" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="E19" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="E20" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="E21" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="E22" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="E23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="E24" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="E25" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="E26" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" ht="64" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="E27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="1" customFormat="1" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="E28" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="E29" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="E30" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="E31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="E32" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="E33" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="B34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="E34" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="B35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="E35" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="B36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="E36" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="E37" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="B38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="E38" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="B39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="E39" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="B40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="E40" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="B41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="E41" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="E42" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="E43" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="1" t="s">
+      <c r="B44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="E44" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="B45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="E45" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="E46" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="E47" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="B48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="E48" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="B49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="E49" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D49" s="1" t="s">
+      <c r="B50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="E50" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" s="1" t="s">
+      <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="E51" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="1" t="s">
+      <c r="B52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="E52" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="B53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="E53" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" s="1" t="s">
+      <c r="B54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="E54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" s="1" t="s">
+      <c r="B55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="E55" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="B56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="1" t="s">
+      <c r="E56" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F55"/>
+  <autoFilter ref="A6:F56" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1"/>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>